--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1737,6 +1737,121 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128742467</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57635</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storö, norra, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577405</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6397919</v>
+      </c>
+      <c r="S12" t="n">
+        <v>125</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1743,7 +1743,7 @@
         <v>128742467</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>57662</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1743,7 +1743,7 @@
         <v>128742467</v>
       </c>
       <c r="B12" t="n">
-        <v>57662</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1743,7 +1743,7 @@
         <v>128742467</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1743,7 +1743,7 @@
         <v>128742467</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>57671</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1743,7 +1743,7 @@
         <v>128742467</v>
       </c>
       <c r="B12" t="n">
-        <v>57671</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1853,6 +1853,210 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129368472</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96130</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>210</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mellanängen, Mellanängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577349</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6397897</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129368071</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577431</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6397928</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96130</v>
+        <v>96146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96146</v>
+        <v>96147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96147</v>
+        <v>96148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96148</v>
+        <v>96152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96152</v>
+        <v>96154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96154</v>
+        <v>96158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96158</v>
+        <v>96166</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96166</v>
+        <v>96169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1858,7 +1858,7 @@
         <v>129368472</v>
       </c>
       <c r="B13" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744576</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122744574</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>122744577</v>
       </c>
       <c r="B4" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>122744593</v>
       </c>
       <c r="B5" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>122744648</v>
       </c>
       <c r="B6" t="n">
-        <v>96531</v>
+        <v>96534</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>122744646</v>
       </c>
       <c r="B7" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>122744643</v>
       </c>
       <c r="B8" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>122744575</v>
       </c>
       <c r="B9" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>122744578</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>122744594</v>
       </c>
       <c r="B11" t="n">
-        <v>91847</v>
+        <v>91850</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744576</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122744574</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>122744577</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>122744593</v>
       </c>
       <c r="B5" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>122744648</v>
       </c>
       <c r="B6" t="n">
-        <v>96534</v>
+        <v>96542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>122744646</v>
       </c>
       <c r="B7" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>122744643</v>
       </c>
       <c r="B8" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>122744575</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>122744578</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>122744594</v>
       </c>
       <c r="B11" t="n">
-        <v>91850</v>
+        <v>91856</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744576</v>
       </c>
       <c r="B2" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122744574</v>
       </c>
       <c r="B3" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>122744577</v>
       </c>
       <c r="B4" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>122744593</v>
       </c>
       <c r="B5" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>122744648</v>
       </c>
       <c r="B6" t="n">
-        <v>96542</v>
+        <v>96552</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>122744646</v>
       </c>
       <c r="B7" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>122744643</v>
       </c>
       <c r="B8" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>122744575</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>122744578</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>122744594</v>
       </c>
       <c r="B11" t="n">
-        <v>91856</v>
+        <v>91866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744576</v>
       </c>
       <c r="B2" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122744574</v>
       </c>
       <c r="B3" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>122744577</v>
       </c>
       <c r="B4" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>122744593</v>
       </c>
       <c r="B5" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>122744648</v>
       </c>
       <c r="B6" t="n">
-        <v>96552</v>
+        <v>96553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>122744646</v>
       </c>
       <c r="B7" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>122744643</v>
       </c>
       <c r="B8" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>122744575</v>
       </c>
       <c r="B9" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>122744578</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>122744594</v>
       </c>
       <c r="B11" t="n">
-        <v>91866</v>
+        <v>91867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744576</v>
       </c>
       <c r="B2" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122744574</v>
       </c>
       <c r="B3" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>122744577</v>
       </c>
       <c r="B4" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>122744648</v>
       </c>
       <c r="B6" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>122744643</v>
       </c>
       <c r="B8" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>122744575</v>
       </c>
       <c r="B9" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>122744578</v>
       </c>
       <c r="B10" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -1305,7 +1305,7 @@
         <v>122744643</v>
       </c>
       <c r="B8" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744576</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122744574</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>122744577</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>122744593</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>91931</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>122744648</v>
       </c>
       <c r="B6" t="n">
-        <v>96554</v>
+        <v>96555</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>122744646</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>122744643</v>
       </c>
       <c r="B8" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>122744575</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>122744578</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>122744594</v>
       </c>
       <c r="B11" t="n">
-        <v>91867</v>
+        <v>91868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744576</v>
       </c>
       <c r="B2" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122744574</v>
       </c>
       <c r="B3" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>122744577</v>
       </c>
       <c r="B4" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>122744593</v>
       </c>
       <c r="B5" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>122744648</v>
       </c>
       <c r="B6" t="n">
-        <v>96555</v>
+        <v>96557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>122744646</v>
       </c>
       <c r="B7" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>122744643</v>
       </c>
       <c r="B8" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>122744575</v>
       </c>
       <c r="B9" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>122744578</v>
       </c>
       <c r="B10" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>122744594</v>
       </c>
       <c r="B11" t="n">
-        <v>91868</v>
+        <v>91870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122744576</v>
       </c>
       <c r="B2" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>122744574</v>
       </c>
       <c r="B3" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>122744577</v>
       </c>
       <c r="B4" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>122744593</v>
       </c>
       <c r="B5" t="n">
-        <v>91933</v>
+        <v>91934</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>122744648</v>
       </c>
       <c r="B6" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>122744646</v>
       </c>
       <c r="B7" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>122744643</v>
       </c>
       <c r="B8" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>122744575</v>
       </c>
       <c r="B9" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>122744578</v>
       </c>
       <c r="B10" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>122744594</v>
       </c>
       <c r="B11" t="n">
-        <v>91870</v>
+        <v>91871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42888-2025 artfynd.xlsx
+++ b/artfynd/A 42888-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744576</v>
+        <v>122744648</v>
       </c>
       <c r="B2" t="n">
-        <v>99125</v>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsjön SÖ, Sm</t>
+          <t>Nybodberget S, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577327</v>
+        <v>577431</v>
       </c>
       <c r="R2" t="n">
-        <v>6398012</v>
+        <v>6397935</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sanna Strömberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -780,48 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744574</v>
+        <v>129368472</v>
       </c>
       <c r="B3" t="n">
-        <v>99125</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsjön SÖ, Sm</t>
+          <t>Mellanängen, Mellanängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577303</v>
+        <v>577349</v>
       </c>
       <c r="R3" t="n">
-        <v>6398003</v>
+        <v>6397897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,12 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -862,71 +865,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sanna Strömberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744577</v>
+        <v>122744589</v>
       </c>
       <c r="B4" t="n">
-        <v>99125</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långsjön SÖ, Sm</t>
+          <t>Hjälmsättra N, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577340</v>
+        <v>577355</v>
       </c>
       <c r="R4" t="n">
-        <v>6397975</v>
+        <v>6397820</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +977,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sanna Strömberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -990,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122744593</v>
+        <v>122744591</v>
       </c>
       <c r="B5" t="n">
-        <v>91938</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +999,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnet S, Sm</t>
+          <t>Enbylehagen S, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577486</v>
+        <v>577364</v>
       </c>
       <c r="R5" t="n">
-        <v>6397872</v>
+        <v>6397826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1069,6 +1070,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1091,45 +1093,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122744648</v>
+        <v>122744595</v>
       </c>
       <c r="B6" t="n">
-        <v>96562</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nybodberget S, Sm</t>
+          <t>Lugnet S, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>577431</v>
       </c>
       <c r="R6" t="n">
-        <v>6397935</v>
+        <v>6397812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,6 +1175,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1181,7 +1187,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Sanna Strömberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1195,7 +1201,7 @@
         <v>122744646</v>
       </c>
       <c r="B7" t="n">
-        <v>91916</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122744643</v>
+        <v>122744585</v>
       </c>
       <c r="B8" t="n">
-        <v>101334</v>
+        <v>96106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,34 +1319,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>2558</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Krushättemossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dunders V, Sm</t>
+          <t>Hjälmsättra N, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577440</v>
+        <v>577371</v>
       </c>
       <c r="R8" t="n">
-        <v>6397826</v>
+        <v>6397709</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,12 +1369,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På hassel.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,48 +1410,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122744575</v>
+        <v>122744592</v>
       </c>
       <c r="B9" t="n">
-        <v>99125</v>
+        <v>96106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2558</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Krushättemossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långsjön SÖ, Sm</t>
+          <t>Enbylehagen S, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577305</v>
+        <v>577322</v>
       </c>
       <c r="R9" t="n">
-        <v>6398015</v>
+        <v>6397899</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,7 +1485,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1497,7 +1496,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sanna Strömberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1508,48 +1507,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744578</v>
+        <v>122744593</v>
       </c>
       <c r="B10" t="n">
-        <v>99125</v>
+        <v>91995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långsjön SÖ, Sm</t>
+          <t>Lugnet S, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577325</v>
+        <v>577486</v>
       </c>
       <c r="R10" t="n">
-        <v>6397967</v>
+        <v>6397872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,12 +1572,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,7 +1586,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1602,7 +1597,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sanna Strömberg</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1616,7 +1611,7 @@
         <v>122744594</v>
       </c>
       <c r="B11" t="n">
-        <v>91875</v>
+        <v>91932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,56 +1713,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128742467</v>
+        <v>129368071</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100067</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storö, norra, Sm</t>
+          <t>Storö, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577405</v>
+        <v>577431</v>
       </c>
       <c r="R12" t="n">
-        <v>6397919</v>
+        <v>6397928</v>
       </c>
       <c r="S12" t="n">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1791,22 +1778,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,22 +1798,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129368472</v>
+        <v>122744588</v>
       </c>
       <c r="B13" t="n">
-        <v>96216</v>
+        <v>5201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,34 +1821,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mellanängen, Mellanängen, Sm</t>
+          <t>Hjälmsättra N, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577349</v>
+        <v>577374</v>
       </c>
       <c r="R13" t="n">
-        <v>6397897</v>
+        <v>6397811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,22 +1875,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,60 +1895,67 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129368071</v>
+        <v>122744574</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storö, Sm</t>
+          <t>Långsjön SÖ, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577431</v>
+        <v>577303</v>
       </c>
       <c r="R14" t="n">
-        <v>6397928</v>
+        <v>6398003</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2005,12 +1979,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,21 +1993,648 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122744575</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långsjön SÖ, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577305</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6398015</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122744576</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långsjön SÖ, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577327</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6398012</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122744577</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långsjön SÖ, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577340</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6397975</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122744578</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långsjön SÖ, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>577325</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6397967</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sanna Strömberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122744642</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dunders V, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>577459</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6397824</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122744643</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dunders V, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>577440</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6397826</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
